--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{250BA9BC-77FE-4EF6-9892-EF0A24F1E6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B910A36-AD13-4AE3-8B49-CDD1CC7084A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Archived" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,11 @@
     <sheet name="WOW &amp; 1st and Last DC Visit" sheetId="13" r:id="rId13"/>
     <sheet name="Workshop Information" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="108">
   <si>
     <t>Archived</t>
   </si>
@@ -72,70 +75,97 @@
     <t>CPD Log for Self</t>
   </si>
   <si>
+    <t>CPD log for self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curriculum </t>
+  </si>
+  <si>
+    <t>Curriculum</t>
+  </si>
+  <si>
     <t>Level 3 Business Administrator</t>
   </si>
   <si>
+    <t>Business Admin Curriculum</t>
+  </si>
+  <si>
     <t>Level 3 Improvement Technician</t>
   </si>
   <si>
+    <t>Improvement Technician Curriculum</t>
+  </si>
+  <si>
     <t>Level 4 AI &amp; Automation</t>
   </si>
   <si>
+    <t>AI &amp; Automation</t>
+  </si>
+  <si>
     <t>Level 4 Associate Project Manager</t>
   </si>
   <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
     <t>Level 5 Improvement Specialist</t>
   </si>
   <si>
+    <t>Improvement Specialist</t>
+  </si>
+  <si>
+    <t>Withdrawn Standards</t>
+  </si>
+  <si>
     <t>Enrollment &amp; Onboarding Learners</t>
   </si>
   <si>
     <t>Client Information When Onboarding</t>
   </si>
   <si>
+    <t>Client information when onboarding</t>
+  </si>
+  <si>
     <t>Email Template for Inviting to Skills Scan</t>
   </si>
   <si>
+    <t>Email template for inviting to Skills Scan</t>
+  </si>
+  <si>
     <t>Presentations for Skills Scan</t>
   </si>
   <si>
     <t>Skills Scans</t>
   </si>
   <si>
+    <t>Getting to Know you tool</t>
+  </si>
+  <si>
+    <t>Getting to know you Tool</t>
+  </si>
+  <si>
     <t>EPA &amp; Apprenticeship Assessment</t>
   </si>
   <si>
     <t>Documents from Coach to Enter Gateway inc Handover</t>
   </si>
   <si>
+    <t>Documents from Coach to enter Gateway inc handover</t>
+  </si>
+  <si>
     <t>DSW Documents &amp; Information</t>
   </si>
   <si>
+    <t>DSW documents &amp; Information</t>
+  </si>
+  <si>
     <t>EPA Handbook (Coach Resource)</t>
   </si>
   <si>
-    <t>L3 Business Administrator Information inc Toolkit</t>
-  </si>
-  <si>
-    <t>L3 Improvement Technician Information &amp; Toolkit</t>
-  </si>
-  <si>
-    <t>L3 Team Leader Information inc Toolkit</t>
-  </si>
-  <si>
-    <t>L4 AI &amp; Automation Information &amp; Toolkit</t>
-  </si>
-  <si>
-    <t>L4 Associate Project Manager inc Toolkit</t>
-  </si>
-  <si>
-    <t>L5 Coaching Information inc Toolkit</t>
-  </si>
-  <si>
-    <t>L5 Improvement Technician Information &amp; Toolkit</t>
-  </si>
-  <si>
-    <t>L5 Operations Manager Information inc Toolkit</t>
+    <t>EPA Handbook ( Coach Resource)</t>
+  </si>
+  <si>
+    <t>Toolkit &amp; Support Materials for Standards</t>
   </si>
   <si>
     <t>Functional Skills</t>
@@ -147,33 +177,51 @@
     <t>English Session Plans and Workshops</t>
   </si>
   <si>
+    <t>English Session plans and Workshops</t>
+  </si>
+  <si>
     <t>Functional Skills Exam Guidance</t>
   </si>
   <si>
     <t>Functional Skills Learning Collective</t>
   </si>
   <si>
+    <t>Functional Skills Log &amp; Feedback</t>
+  </si>
+  <si>
     <t>Functional Skills Log</t>
   </si>
   <si>
     <t>Maths Session Plans and Workshops</t>
   </si>
   <si>
+    <t>Maths Session plans and Workshops</t>
+  </si>
+  <si>
     <t>Inclusion</t>
   </si>
   <si>
-    <t>Guides and Launch Documents</t>
+    <t>Guides and  Documents</t>
+  </si>
+  <si>
+    <t>Guides &amp; Documents</t>
   </si>
   <si>
     <t>Learning Collective and Learner Tools</t>
   </si>
   <si>
+    <t>Learning Collective &amp; Learner Tools</t>
+  </si>
+  <si>
     <t>Training Presentations &amp; Resources</t>
   </si>
   <si>
     <t>On Programme - Coaches</t>
   </si>
   <si>
+    <t>On Programme support for Coaches</t>
+  </si>
+  <si>
     <t>Action Planning</t>
   </si>
   <si>
@@ -183,6 +231,9 @@
     <t>Email Templates for Sessions &amp; Deadlines</t>
   </si>
   <si>
+    <t>Email templates for sessions &amp; deadlines</t>
+  </si>
+  <si>
     <t>Functional Skills Logs</t>
   </si>
   <si>
@@ -192,15 +243,24 @@
     <t>Personal, Professional &amp; Educational Support</t>
   </si>
   <si>
+    <t>Personal, Professional &amp; Educational support</t>
+  </si>
+  <si>
     <t>Pre-loved Coach Handover</t>
   </si>
   <si>
+    <t>Pre loved Coach handover</t>
+  </si>
+  <si>
     <t>Progress Review &amp; TLA Questions inc Safeguarding</t>
   </si>
   <si>
     <t>Shadowing &amp; Mentoring Logs</t>
   </si>
   <si>
+    <t>Ai Tips &amp; Tricks</t>
+  </si>
+  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -219,9 +279,15 @@
     <t>Safeguarding</t>
   </si>
   <si>
+    <t>Safeguarding Folder</t>
+  </si>
+  <si>
     <t>Safeguarding Induction for New Coaches</t>
   </si>
   <si>
+    <t>Safeguarding Induction for new Coaches</t>
+  </si>
+  <si>
     <t>Safeguarding Newsletters</t>
   </si>
   <si>
@@ -231,134 +297,89 @@
     <t>Safeguarding Support for Learners</t>
   </si>
   <si>
+    <t>Safeguarding support for learners</t>
+  </si>
+  <si>
     <t>Safeguarding Team</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Client Handbook in Contract Onboarding</t>
+    <t>Sales Channel</t>
+  </si>
+  <si>
+    <t>Client Handbook &amp; Contract</t>
+  </si>
+  <si>
+    <t>Client Handbook &amp; Contracts</t>
   </si>
   <si>
     <t>Overview Packs for Employers</t>
   </si>
   <si>
+    <t>Overview Pack for Employers</t>
+  </si>
+  <si>
     <t>Overview Packs for Learners</t>
   </si>
   <si>
+    <t>Overview packs for Learners</t>
+  </si>
+  <si>
     <t>Pitch Pack</t>
   </si>
   <si>
+    <t>Learner Briefing Videos</t>
+  </si>
+  <si>
+    <t>Learner Briefing videos</t>
+  </si>
+  <si>
     <t>Useful Links &amp; Info</t>
   </si>
   <si>
+    <t>useful links &amp; info</t>
+  </si>
+  <si>
     <t>Apprentice of the Month</t>
   </si>
   <si>
     <t>Learner Portal (De-funded Standards)</t>
   </si>
   <si>
+    <t>Learner Portal ( de-funded standards)</t>
+  </si>
+  <si>
     <t>Out of Office Messages for All Learner Facing</t>
   </si>
   <si>
+    <t>Out of Office Messages for all learner facing</t>
+  </si>
+  <si>
     <t>WOW &amp; 1st and Last DC Visit</t>
   </si>
   <si>
+    <t>WOW &amp; 1st and last DC visits</t>
+  </si>
+  <si>
+    <t>Level 4 Ai &amp; Automation</t>
+  </si>
+  <si>
     <t>Withdrawn Apprenticeships</t>
   </si>
   <si>
     <t>Workshop Information</t>
   </si>
   <si>
-    <t>WOW &amp; 1st and last DC visits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curriculum </t>
-  </si>
-  <si>
-    <t>Curriculum</t>
-  </si>
-  <si>
-    <t>Business Admin Curriculum</t>
-  </si>
-  <si>
-    <t>Improvement Technician Curriculum</t>
-  </si>
-  <si>
-    <t>AI &amp; Automation</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>Improvement Specialist</t>
-  </si>
-  <si>
-    <t>Safeguarding Folder</t>
-  </si>
-  <si>
-    <t>Safeguarding Induction for new Coaches</t>
-  </si>
-  <si>
-    <t>Safeguarding support for learners</t>
-  </si>
-  <si>
-    <t>Documents from Coach to enter Gateway inc handover</t>
-  </si>
-  <si>
-    <t>DSW documents &amp; Information</t>
-  </si>
-  <si>
-    <t>EPA Handbook ( Coach Resource)</t>
-  </si>
-  <si>
-    <t>L3 Business Administrator information inc Toolkit</t>
-  </si>
-  <si>
-    <t>L3 Improvement Technician information &amp; Toolkit</t>
-  </si>
-  <si>
-    <t>L3 Team Leader information inc Toolkit</t>
-  </si>
-  <si>
-    <t>L4 Ai &amp; Automation information &amp; Toolkit</t>
-  </si>
-  <si>
-    <t>L5 Coaching information inc Toolkit</t>
-  </si>
-  <si>
-    <t>L5 Improvement Technician information &amp;Toolkit</t>
-  </si>
-  <si>
-    <t>L5 Operations Manager information inc Toolkit</t>
-  </si>
-  <si>
-    <t>English Session plans and Workshops</t>
-  </si>
-  <si>
-    <t>Maths Session plans and Workshops</t>
-  </si>
-  <si>
-    <t>On Programme support for Coaches</t>
-  </si>
-  <si>
-    <t>Email templates for sessions &amp; deadlines</t>
-  </si>
-  <si>
-    <t>Personal, Professional &amp; Educational support</t>
-  </si>
-  <si>
-    <t>Pre loved Coach handover</t>
-  </si>
-  <si>
-    <t>Ai Tips &amp; Tricks</t>
+    <t>Schedule for Workshops</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,7 +483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -486,8 +507,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -792,21 +816,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -817,7 +841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -835,22 +859,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -861,59 +885,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -931,22 +955,23 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -957,46 +982,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
+        <f t="shared" ref="A4:A8" si="0">ROW() - ROW($A$4) + 1</f>
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{AA3355EA-4A04-47EC-98BC-0456234FFD99}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{667D8484-83A4-4E1C-B14A-555E4B7476ED}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{6F9F5A23-ABFD-4AA1-9CC2-BEC8704EC810}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{AD4E5E99-1FAD-4660-84C1-9F9166A42BEF}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{EDED66D4-8853-4797-A97C-6541286E5A87}"/>
+    <hyperlink ref="C4" r:id="rId6" xr:uid="{4E4649B3-C213-40B1-8BDE-D7582C82FCFB}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1004,21 +1058,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1029,37 +1084,46 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{C1734F1A-AFA8-40F2-8AD0-243A287BDD26}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{9B4898A0-D61F-4BC8-83C0-77B3E83C6FAE}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{DF50744B-48B9-4AE9-ABAD-94D5FB781EEF}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{3252E722-EECE-4145-9D53-8AE1031F300B}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1067,22 +1131,22 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1093,63 +1157,82 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <f t="shared" ref="C4:C9" si="0">PROPER(_xlfn.TEXTBEFORE(B4, " ", 1) &amp; MID(B4, FIND(" ", B4), 12) &amp; MID(LEFT(B4, 22), FIND("{token}", SUBSTITUTE(B4, " ", "{token}", 3)) + 1, LEN(B4)) &amp; MID(B4, LEN(B4) - 6, 3) &amp; RIGHT(B4, 4))</f>
+        <v>Level 3 Business Adminstrator</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>105</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgABCZboBEw2T5bnTLmjlPb5AYTrjqKFnQO570YOajKeyEU?e=9iCrno" xr:uid="{05A5D8A3-E196-4BC4-AF1E-D8E62ACD8188}"/>
+    <hyperlink ref="C4" r:id="rId2" display="Level 3 Business Adminstrator" xr:uid="{F7F67A53-F356-4F27-B444-3D66BED5A5D8}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{0EC652D1-0AB6-4D6D-ABF0-27B43C0B0247}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{5B5C14B3-5630-4A3C-9E8A-4CDCDD575FDE}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{82483623-C930-41C3-94AE-0363D4FAAD3E}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{80C4505B-592B-4064-BF87-1A5130A9CC41}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{27712CD2-53C2-4F0E-B221-7D6449B13DD6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1158,21 +1241,21 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1183,39 +1266,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{3B24DC08-4D3C-4722-BE2D-D8DDB1081D9B}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1226,51 +1317,62 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{B0001841-3AC6-4463-AF1E-980F6FCD90F3}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{C0AAEB82-9420-4739-9D90-6E4F77D5F880}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{47326CD7-6175-4F48-B27C-A75BE5BFB581}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1281,59 +1383,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>81</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1344,6 +1457,7 @@
     <hyperlink ref="C6" r:id="rId4" xr:uid="{0FB98658-E883-453F-A3D9-133B90056D21}"/>
     <hyperlink ref="C7" r:id="rId5" xr:uid="{B6028A25-B007-4D43-8C00-C7741E46B35E}"/>
     <hyperlink ref="C8" r:id="rId6" xr:uid="{D0DC23D0-A906-4016-8B1B-F71F34B948C9}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{2067006F-466D-4DD7-82F7-42B51853397A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1351,22 +1465,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1377,69 +1492,93 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{328BCA09-A293-447B-BDB0-ED054FF6E59B}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{8310A051-6953-414F-9564-CFA5DD7524D9}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{AD9AA705-07F6-40C7-9972-E09DAA4B5E35}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{1D891557-A5C9-4D46-9808-CE360F0F1100}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{EB0A6431-DBA5-4031-A7F0-56838D8A3207}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{AED1AA7F-8793-4342-B6C7-47A714DE4ECF}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1450,125 +1589,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
+      <c r="B7" t="s">
+        <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1577,14 +1639,7 @@
     <hyperlink ref="C1" r:id="rId2" xr:uid="{B0767483-3105-421D-BD9B-2360A6854D4D}"/>
     <hyperlink ref="C5" r:id="rId3" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgD77hFdLdF4S6KLQBjYmr1dAbcasBbaT0Td_HxIYq3HUQ0?e=JNZUUV" xr:uid="{DE3279D9-A31E-4572-96F5-F034C561735B}"/>
     <hyperlink ref="C6" r:id="rId4" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgAU-7qsQnYTTaLo47q_CBipAWFgc1UcyixpGYSUy0zIpE4?e=SX6a0b" xr:uid="{C16EEEED-128A-4844-8DAF-CAB1FAE63D70}"/>
-    <hyperlink ref="C7" r:id="rId5" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgCO5u6aXnM0Ro_gxt8UF_3sAYI_KVorW5xja4EoZCVFssQ?e=IRdmOc" xr:uid="{A5E07C03-D745-4BB9-8B0B-94E61CF76527}"/>
-    <hyperlink ref="C8" r:id="rId6" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgAeBnYbFh34SpXT2uZxGrdJAT3gedJh9OV9Er8VW9BixD8?e=RQQ6hS" xr:uid="{EEDD860D-9805-49A2-88DD-264E0A89969F}"/>
-    <hyperlink ref="C9" r:id="rId7" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgCXaVg_5gfwRK6nFKsicxeZAYCct6bGao4q3Z-KRLMviMk?e=kRD69G" xr:uid="{085BBBEA-4038-49BB-9D2D-F5A64FF5963E}"/>
-    <hyperlink ref="C10" r:id="rId8" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgBqdwKUqcvXQ6Iydxw5MouHAeFVPmrvOXLzZSwrJ1ulghY?e=P9Qg8x" xr:uid="{797720F9-5EE6-49E4-B799-93B7710B5DD2}"/>
-    <hyperlink ref="C11" r:id="rId9" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgBAIielOdXYTb1ttMZx18lrAfHnBj9TGxoFnkgkIwuT0mk?e=imaJI9" xr:uid="{C9D8605F-B71E-4A01-94E9-30A2FD96DFC2}"/>
-    <hyperlink ref="C12" r:id="rId10" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgDXbq0O-lswRpVGqtz14WQMASno916-44ZwJpSwmUcHisk?e=rVeYtd" xr:uid="{90A0F937-71B9-46B7-880B-7B9E45905CB6}"/>
-    <hyperlink ref="C13" r:id="rId11" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgCdMNAv3B1oR4y50tOhzx2NAVjOBFoj2SP5iZ2jdH_iQuI?e=Ntwj37" xr:uid="{660EB4E9-99C6-4B94-9D41-708B16037710}"/>
-    <hyperlink ref="C14" r:id="rId12" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgDRrYbuSKmcRKB0kLe-Hhb0AbEWBJmLAJ9sAtX_yp_LDhs?e=XwtaRX" xr:uid="{9C471AFE-F697-461C-B3B8-346C2C364433}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{DE97569F-B519-4432-9E17-EE8BBDB743B7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1593,22 +1648,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1619,70 +1674,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1702,21 +1757,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1727,37 +1782,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{2065DB81-8103-4121-ABA1-ACABF7D52725}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{7572CC62-D8E9-4DF2-99AA-91FC0489422A}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{848A7938-5940-4194-9AA0-7CEC12D8DCAC}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1765,22 +1831,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1791,111 +1857,111 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="4">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="4">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="4">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="B13" s="10" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1919,21 +1985,22 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1944,46 +2011,247 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{4FF5D541-D3FA-4478-8D58-FF4C16CB32F4}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{F8522559-A115-4545-9D42-3777419A3AE1}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{3230A60B-DD21-43B8-BF55-F5E7019EB2BF}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{1848D702-AA07-4DE4-A921-9D408190C8BE}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{1E5D9B68-AB5C-48E8-BBFD-A5178D2FF1EC}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D7BC0CAF3344154CA74557FF433B0E52" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1eaa4a0b6d4ef4834ba44704c91852be">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e978c516-ea6f-42b5-a167-b4419a4db07c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511bb21f8a7d14895ec12dd82944ac79" ns2:_="">
+    <xsd:import namespace="e978c516-ea6f-42b5-a167-b4419a4db07c"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e978c516-ea6f-42b5-a167-b4419a4db07c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7333649C-E6E2-4480-9B5F-AB2B2D15A42B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
 </file>
--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B910A36-AD13-4AE3-8B49-CDD1CC7084A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{760E4E58-EA34-489B-ADB3-87354E068883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Archived" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="110">
   <si>
     <t>Archived</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>Ai Tips &amp; Tricks</t>
+  </si>
+  <si>
+    <t>Getting to know you tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Getting to Know you </t>
   </si>
   <si>
     <t>Quality</t>
@@ -379,7 +385,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,8 +516,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -816,21 +822,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -841,7 +847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -859,22 +865,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -885,59 +891,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -956,22 +962,22 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -982,64 +988,64 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <f t="shared" ref="A4:A8" si="0">ROW() - ROW($A$4) + 1</f>
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1058,22 +1064,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1084,37 +1090,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1131,22 +1137,22 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1157,7 +1163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1165,11 +1171,11 @@
         <v>11</v>
       </c>
       <c r="C4" s="6" t="str">
-        <f t="shared" ref="C4:C9" si="0">PROPER(_xlfn.TEXTBEFORE(B4, " ", 1) &amp; MID(B4, FIND(" ", B4), 12) &amp; MID(LEFT(B4, 22), FIND("{token}", SUBSTITUTE(B4, " ", "{token}", 3)) + 1, LEN(B4)) &amp; MID(B4, LEN(B4) - 6, 3) &amp; RIGHT(B4, 4))</f>
+        <f t="shared" ref="C4" si="0">PROPER(_xlfn.TEXTBEFORE(B4, " ", 1) &amp; MID(B4, FIND(" ", B4), 12) &amp; MID(LEFT(B4, 22), FIND("{token}", SUBSTITUTE(B4, " ", "{token}", 3)) + 1, LEN(B4)) &amp; MID(B4, LEN(B4) - 6, 3) &amp; RIGHT(B4, 4))</f>
         <v>Level 3 Business Adminstrator</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1188,10 +1194,10 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1213,15 +1219,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1241,21 +1247,21 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1266,15 +1272,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1291,14 +1297,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -1306,7 +1312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1317,7 +1323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1328,7 +1334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1339,7 +1345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1357,14 +1363,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -1372,7 +1378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1383,7 +1389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1394,7 +1400,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1405,7 +1411,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1416,7 +1422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1427,7 +1433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1438,7 +1444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1466,14 +1472,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
@@ -1481,7 +1487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1514,7 +1520,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1563,14 +1569,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>31</v>
       </c>
@@ -1578,7 +1584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1600,7 +1606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1611,7 +1617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1622,7 +1628,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1648,14 +1654,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -1663,7 +1669,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1674,7 +1680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1685,7 +1691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1696,7 +1702,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1707,7 +1713,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1729,7 +1735,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1757,21 +1763,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1782,7 +1788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1793,7 +1799,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1804,7 +1810,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1830,15 +1836,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>55</v>
       </c>
@@ -1846,7 +1852,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1857,7 +1863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1879,7 +1885,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1901,7 +1907,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1923,7 +1929,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -1934,7 +1940,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -1945,7 +1951,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -1956,12 +1962,26 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
       <c r="B13" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1977,6 +1997,7 @@
     <hyperlink ref="C11" r:id="rId9" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgCt038vgOD0R7aaxXbOAPhJAThpFIdOsAA3MhtT91Xf6cE?e=afH8mY" xr:uid="{6D70FB7F-38A7-459D-9EBB-587F3D2CE535}"/>
     <hyperlink ref="C12" r:id="rId10" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgDaqzXZ_ZJnTrnHhKWIVpakAeGE4b9eY0XS-sG54GRTDbo?e=JCfLtN" xr:uid="{378D1042-D627-4F88-AA2A-2CAD4EF7FCB5}"/>
     <hyperlink ref="C13" r:id="rId11" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgAku8nbCSyfS6Ln_gvcposBAUgs2yHG4Kr7Xbeen6ncunQ?e=JUGhgd" xr:uid="{4ECDD234-5273-4F18-B0B9-ED0E25F9019E}"/>
+    <hyperlink ref="C14" r:id="rId12" xr:uid="{024BA66F-BE3F-4977-AA79-23DC126A3BEE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1985,22 +2006,22 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2011,48 +2032,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2068,8 +2089,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D7BC0CAF3344154CA74557FF433B0E52" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1eaa4a0b6d4ef4834ba44704c91852be">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e978c516-ea6f-42b5-a167-b4419a4db07c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511bb21f8a7d14895ec12dd82944ac79" ns2:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D7BC0CAF3344154CA74557FF433B0E52" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22ce74f56774179b6aa44b16d17f214e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e978c516-ea6f-42b5-a167-b4419a4db07c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="803c41c4820f50a4bf0f10a50d795b38" ns2:_="">
     <xsd:import namespace="e978c516-ea6f-42b5-a167-b4419a4db07c"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -2084,6 +2120,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2127,6 +2164,11 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="15" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2229,29 +2271,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7333649C-E6E2-4480-9B5F-AB2B2D15A42B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7828DA5C-45CF-41E1-9BB1-6DBD5EA666FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e978c516-ea6f-42b5-a167-b4419a4db07c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{760E4E58-EA34-489B-ADB3-87354E068883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2984C59A-1E55-4F59-BFEF-9C73D2DC6BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Archived" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="117">
   <si>
     <t>Archived</t>
   </si>
@@ -198,6 +198,9 @@
     <t>Maths Session plans and Workshops</t>
   </si>
   <si>
+    <t>Functional Skills Calendar</t>
+  </si>
+  <si>
     <t>Inclusion</t>
   </si>
   <si>
@@ -267,6 +270,18 @@
     <t xml:space="preserve">Getting to Know you </t>
   </si>
   <si>
+    <t>Learning Collectives inc Women in Leadership</t>
+  </si>
+  <si>
+    <t>Learning Collectives inc WIL</t>
+  </si>
+  <si>
+    <t>Bud</t>
+  </si>
+  <si>
+    <t>Processes</t>
+  </si>
+  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -282,6 +297,9 @@
     <t>Quality Strategy &amp; Process Overviews</t>
   </si>
   <si>
+    <t>Learner Walks</t>
+  </si>
+  <si>
     <t>Safeguarding</t>
   </si>
   <si>
@@ -315,7 +333,7 @@
     <t>Sales Channel</t>
   </si>
   <si>
-    <t>Client Handbook &amp; Contract</t>
+    <t>Client info (inc Handbook,forms &amp; Contract)</t>
   </si>
   <si>
     <t>Client Handbook &amp; Contracts</t>
@@ -340,6 +358,9 @@
   </si>
   <si>
     <t>Learner Briefing videos</t>
+  </si>
+  <si>
+    <t>Example documentation from Bud</t>
   </si>
   <si>
     <t>Useful Links &amp; Info</t>
@@ -385,7 +406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,8 +537,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -822,21 +843,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -847,7 +868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -865,22 +886,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -891,59 +912,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -961,23 +982,23 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -988,64 +1009,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <f t="shared" ref="A4:A8" si="0">ROW() - ROW($A$4) + 1</f>
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1056,6 +1088,7 @@
     <hyperlink ref="C6" r:id="rId4" xr:uid="{AD4E5E99-1FAD-4660-84C1-9F9166A42BEF}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{EDED66D4-8853-4797-A97C-6541286E5A87}"/>
     <hyperlink ref="C4" r:id="rId6" xr:uid="{4E4649B3-C213-40B1-8BDE-D7582C82FCFB}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{FF1C053D-DBEE-4F3D-B61A-6A1FAE510A28}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1064,22 +1097,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1090,37 +1123,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1137,22 +1170,22 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1163,7 +1196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1171,11 +1204,11 @@
         <v>11</v>
       </c>
       <c r="C4" s="6" t="str">
-        <f t="shared" ref="C4" si="0">PROPER(_xlfn.TEXTBEFORE(B4, " ", 1) &amp; MID(B4, FIND(" ", B4), 12) &amp; MID(LEFT(B4, 22), FIND("{token}", SUBSTITUTE(B4, " ", "{token}", 3)) + 1, LEN(B4)) &amp; MID(B4, LEN(B4) - 6, 3) &amp; RIGHT(B4, 4))</f>
+        <f t="shared" ref="C4:C9" si="0">PROPER(_xlfn.TEXTBEFORE(B4, " ", 1) &amp; MID(B4, FIND(" ", B4), 12) &amp; MID(LEFT(B4, 22), FIND("{token}", SUBSTITUTE(B4, " ", "{token}", 3)) + 1, LEN(B4)) &amp; MID(B4, LEN(B4) - 6, 3) &amp; RIGHT(B4, 4))</f>
         <v>Level 3 Business Adminstrator</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1186,7 +1219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1194,10 +1227,10 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1208,7 +1241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1219,15 +1252,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1247,21 +1280,21 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1272,15 +1305,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1297,14 +1330,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -1312,7 +1345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1323,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1334,7 +1367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1345,7 +1378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1363,14 +1396,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -1378,7 +1411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1389,7 +1422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1400,7 +1433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1411,7 +1444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1422,7 +1455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1433,7 +1466,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1444,7 +1477,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1472,14 +1505,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
@@ -1487,7 +1520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1498,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1509,7 +1542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1520,7 +1553,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1531,7 +1564,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1542,7 +1575,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1569,14 +1602,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="9" t="s">
         <v>31</v>
       </c>
@@ -1584,7 +1617,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1595,7 +1628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1606,7 +1639,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1617,7 +1650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1628,7 +1661,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1653,15 +1686,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -1669,7 +1702,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1680,7 +1713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1691,7 +1724,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1702,7 +1735,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1713,7 +1746,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1724,7 +1757,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1735,7 +1768,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1744,6 +1777,17 @@
       </c>
       <c r="C9" s="6" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1755,6 +1799,7 @@
     <hyperlink ref="C7" r:id="rId5" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgAQoiwZa3qFS6i2aIlc7UVIAcMpa73M5PEgf83CW1gzpgc?e=ECWooE" xr:uid="{7318B6C3-C8A4-43E0-80B0-DDDD0F2C8F6A}"/>
     <hyperlink ref="C8" r:id="rId6" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgBz8n2lo9L0QKC7gXF9FjGPAVHfUbRuEw7dpfil0po2Yms?e=OsMIXY" xr:uid="{93996F1D-2827-4203-8AEA-E57EA9C271AB}"/>
     <hyperlink ref="C9" r:id="rId7" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgDaDaR3CH2ISJ3yFB7tNkJjAQPuSS6bKYblFtBv6cTypyw?e=c7cQm7" xr:uid="{F921B032-DC56-43A3-95BC-3B6562104947}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{4E1A4083-FC8A-4F13-AAFD-BE2B099A850F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1763,21 +1808,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1788,37 +1833,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1836,23 +1881,23 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1863,125 +1908,158 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="4">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="4">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="4">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1998,6 +2076,9 @@
     <hyperlink ref="C12" r:id="rId10" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgDaqzXZ_ZJnTrnHhKWIVpakAeGE4b9eY0XS-sG54GRTDbo?e=JCfLtN" xr:uid="{378D1042-D627-4F88-AA2A-2CAD4EF7FCB5}"/>
     <hyperlink ref="C13" r:id="rId11" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgAku8nbCSyfS6Ln_gvcposBAUgs2yHG4Kr7Xbeen6ncunQ?e=JUGhgd" xr:uid="{4ECDD234-5273-4F18-B0B9-ED0E25F9019E}"/>
     <hyperlink ref="C14" r:id="rId12" xr:uid="{024BA66F-BE3F-4977-AA79-23DC126A3BEE}"/>
+    <hyperlink ref="C15" r:id="rId13" xr:uid="{C2171F9A-1AD8-4C05-9832-B44B4560DCA1}"/>
+    <hyperlink ref="C16" r:id="rId14" xr:uid="{66537494-3DB2-4DDA-B5A8-9F92004CF025}"/>
+    <hyperlink ref="C17" r:id="rId15" xr:uid="{97367CA0-4521-40F4-9D69-CE2ABE8F3532}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2005,23 +2086,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2032,48 +2113,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2083,27 +2175,13 @@
     <hyperlink ref="C5" r:id="rId3" xr:uid="{3230A60B-DD21-43B8-BF55-F5E7019EB2BF}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{1848D702-AA07-4DE4-A921-9D408190C8BE}"/>
     <hyperlink ref="C7" r:id="rId5" xr:uid="{1E5D9B68-AB5C-48E8-BBFD-A5178D2FF1EC}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{3D961F96-E075-4E02-93E0-A535C3373DEF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D7BC0CAF3344154CA74557FF433B0E52" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22ce74f56774179b6aa44b16d17f214e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e978c516-ea6f-42b5-a167-b4419a4db07c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="803c41c4820f50a4bf0f10a50d795b38" ns2:_="">
     <xsd:import namespace="e978c516-ea6f-42b5-a167-b4419a4db07c"/>
@@ -2271,37 +2349,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7828DA5C-45CF-41E1-9BB1-6DBD5EA666FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7828DA5C-45CF-41E1-9BB1-6DBD5EA666FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e978c516-ea6f-42b5-a167-b4419a4db07c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
 </file>
--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2984C59A-1E55-4F59-BFEF-9C73D2DC6BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85DC6C5A-06AB-4FFD-A00B-505283BD88B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Archived" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="Useful Links &amp; Info" sheetId="12" r:id="rId12"/>
     <sheet name="WOW &amp; 1st and Last DC Visit" sheetId="13" r:id="rId13"/>
     <sheet name="Workshop Information" sheetId="14" r:id="rId14"/>
+    <sheet name="Meeting  Documents" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="123">
   <si>
     <t>Archived</t>
   </si>
@@ -201,6 +202,12 @@
     <t>Functional Skills Calendar</t>
   </si>
   <si>
+    <t>SLC booking &amp; Documents</t>
+  </si>
+  <si>
+    <t>SLC Booking &amp; Documents</t>
+  </si>
+  <si>
     <t>Inclusion</t>
   </si>
   <si>
@@ -400,6 +407,18 @@
   </si>
   <si>
     <t>Schedule for Workshops</t>
+  </si>
+  <si>
+    <t>Meeting Documents</t>
+  </si>
+  <si>
+    <t>Team Meetings</t>
+  </si>
+  <si>
+    <t>Standardisations</t>
+  </si>
+  <si>
+    <t>Working Groups</t>
   </si>
 </sst>
 </file>
@@ -895,10 +914,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -917,10 +936,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -928,10 +947,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -939,10 +958,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -950,10 +969,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -961,10 +980,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -992,10 +1011,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -1015,10 +1034,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1027,10 +1046,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1039,10 +1058,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1051,10 +1070,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1063,10 +1082,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1074,10 +1093,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1106,10 +1125,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -1128,10 +1147,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1139,10 +1158,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1150,10 +1169,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1179,10 +1198,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -1227,7 +1246,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1257,10 +1276,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1289,7 +1308,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1310,10 +1329,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1324,6 +1343,94 @@
     <hyperlink ref="C4" r:id="rId1" xr:uid="{3B24DC08-4D3C-4722-BE2D-D8DDB1081D9B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12DC13A-935D-4610-B520-0A9E50ED6B6C}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{E5F55F04-D1D5-401F-8E88-1EC494F165B2}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{01F93AC5-DE33-4034-A6C4-9660D4E2518F}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{DE974895-83A9-49AD-BBBD-3ACE76459B00}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{0549BCE7-16A2-4FA7-8E8F-7BFAB3F8FFE3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1686,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1790,6 +1897,17 @@
         <v>49</v>
       </c>
     </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgASABH9Rx0zSKM7JWFkjAEuAeduW9zNeWxSKQsRTc0g3qc?e=Wn9usE" xr:uid="{DBFC80BD-A1CD-4AAA-9233-E84B496AAC56}"/>
@@ -1800,6 +1918,7 @@
     <hyperlink ref="C8" r:id="rId6" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgBz8n2lo9L0QKC7gXF9FjGPAVHfUbRuEw7dpfil0po2Yms?e=OsMIXY" xr:uid="{93996F1D-2827-4203-8AEA-E57EA9C271AB}"/>
     <hyperlink ref="C9" r:id="rId7" display="https://raisethebarltd.sharepoint.com/:f:/s/UsefulinformationinApprenticeships/IgDaDaR3CH2ISJ3yFB7tNkJjAQPuSS6bKYblFtBv6cTypyw?e=c7cQm7" xr:uid="{F921B032-DC56-43A3-95BC-3B6562104947}"/>
     <hyperlink ref="C10" r:id="rId8" xr:uid="{4E1A4083-FC8A-4F13-AAFD-BE2B099A850F}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{3A83CC27-8339-441B-BACE-3C787BABDACF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1817,7 +1936,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1838,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1849,10 +1968,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1860,10 +1979,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1891,10 +2010,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -1913,10 +2032,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1924,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1935,10 +2054,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1946,10 +2065,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1957,10 +2076,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1968,10 +2087,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1979,10 +2098,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1990,10 +2109,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2001,10 +2120,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2012,10 +2131,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2023,10 +2142,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2034,10 +2153,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2045,10 +2164,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2056,10 +2175,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2096,10 +2215,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -2118,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2129,10 +2248,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2140,10 +2259,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2151,10 +2270,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2162,10 +2281,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2182,9 +2301,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D7BC0CAF3344154CA74557FF433B0E52" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22ce74f56774179b6aa44b16d17f214e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e978c516-ea6f-42b5-a167-b4419a4db07c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="803c41c4820f50a4bf0f10a50d795b38" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D7BC0CAF3344154CA74557FF433B0E52" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b54d75a50ac64c6661fb4f92022cbcf2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e978c516-ea6f-42b5-a167-b4419a4db07c" xmlns:ns3="80b4c68b-5b71-4f83-9896-bd34d2f876c2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="513583b2c4d71f01c14400ece81cb5d3" ns2:_="" ns3:_="">
     <xsd:import namespace="e978c516-ea6f-42b5-a167-b4419a4db07c"/>
+    <xsd:import namespace="80b4c68b-5b71-4f83-9896-bd34d2f876c2"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2199,6 +2319,9 @@
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2248,6 +2371,35 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="820d2062-da2e-4a86-b6fb-103b3a895a4c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="80b4c68b-5b71-4f83-9896-bd34d2f876c2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c1084db9-4940-436b-8ee7-52899cb44650}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="80b4c68b-5b71-4f83-9896-bd34d2f876c2">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2350,12 +2502,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2364,14 +2510,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e978c516-ea6f-42b5-a167-b4419a4db07c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="80b4c68b-5b71-4f83-9896-bd34d2f876c2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7828DA5C-45CF-41E1-9BB1-6DBD5EA666FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C52F9FD8-98F0-4A3F-B70F-491091A64C54}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
 </file>
--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85DC6C5A-06AB-4FFD-A00B-505283BD88B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65FAFE3E-FD96-404D-BA2D-9D0339F5280E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Archived" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="WOW &amp; 1st and Last DC Visit" sheetId="13" r:id="rId13"/>
     <sheet name="Workshop Information" sheetId="14" r:id="rId14"/>
     <sheet name="Meeting  Documents" sheetId="15" r:id="rId15"/>
+    <sheet name="RTB Benefits" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="127">
   <si>
     <t>Archived</t>
   </si>
@@ -419,6 +420,18 @@
   </si>
   <si>
     <t>Working Groups</t>
+  </si>
+  <si>
+    <t>Ofsted Sessions</t>
+  </si>
+  <si>
+    <t>Agenda summary</t>
+  </si>
+  <si>
+    <t>RTB Benefits</t>
+  </si>
+  <si>
+    <t>RTB Benefits for the team</t>
   </si>
 </sst>
 </file>
@@ -529,7 +542,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -555,6 +568,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -870,11 +886,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
@@ -1307,11 +1323,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
@@ -1409,13 +1425,21 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:3">
@@ -1429,6 +1453,35 @@
     <hyperlink ref="C5" r:id="rId2" xr:uid="{01F93AC5-DE33-4034-A6C4-9660D4E2518F}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{DE974895-83A9-49AD-BBBD-3ACE76459B00}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{0549BCE7-16A2-4FA7-8E8F-7BFAB3F8FFE3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A46757-BEDB-41F7-9725-069D11C48F1E}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" xr:uid="{5E3E0292-EBCA-4FB5-8011-C88A49A52CAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1935,11 +1988,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
@@ -2502,15 +2555,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="e978c516-ea6f-42b5-a167-b4419a4db07c">
@@ -2521,14 +2565,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C52F9FD8-98F0-4A3F-B70F-491091A64C54}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B9C383-E321-44F2-8A34-04799A5EDA7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABFAA37-DD12-4A2A-A8A9-2E90E5F5015F}"/>
 </file>
--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65FAFE3E-FD96-404D-BA2D-9D0339F5280E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{710EC2C4-C3FF-43D2-B694-5DDD28481726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Archived" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="133">
   <si>
     <t>Archived</t>
   </si>
@@ -432,6 +432,24 @@
   </si>
   <si>
     <t>RTB Benefits for the team</t>
+  </si>
+  <si>
+    <t>subfolder</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Discount for Teachers ( all can use)</t>
+  </si>
+  <si>
+    <t>Discount for Teachers</t>
+  </si>
+  <si>
+    <t>YuLife Rewards</t>
+  </si>
+  <si>
+    <t>Yulife</t>
   </si>
 </sst>
 </file>
@@ -1460,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A46757-BEDB-41F7-9725-069D11C48F1E}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1476,12 +1494,38 @@
         <v>126</v>
       </c>
     </row>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G1" r:id="rId1" xr:uid="{5E3E0292-EBCA-4FB5-8011-C88A49A52CAB}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{A5CF5EA8-E5EC-4880-9A17-C2F3527CEEB6}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{F090F27F-0EE8-48DE-8038-D745A1B26C20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Useful_Information_for_Apprenticeships.xlsx
+++ b/Useful_Information_for_Apprenticeships.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janette Healey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{710EC2C4-C3FF-43D2-B694-5DDD28481726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87E85F2B-2B55-43AF-ABA3-FAAE3882D8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="134">
   <si>
     <t>Archived</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>Agenda summary</t>
+  </si>
+  <si>
+    <t>Agenda</t>
   </si>
   <si>
     <t>RTB Benefits</t>
@@ -1449,7 +1452,9 @@
       <c r="B7" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4">
@@ -1458,7 +1463,9 @@
       <c r="B8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4"/>
@@ -1471,6 +1478,8 @@
     <hyperlink ref="C5" r:id="rId2" xr:uid="{01F93AC5-DE33-4034-A6C4-9660D4E2518F}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{DE974895-83A9-49AD-BBBD-3ACE76459B00}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{0549BCE7-16A2-4FA7-8E8F-7BFAB3F8FFE3}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{E0129F63-0333-45AC-A15B-8709903448F2}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{A4F5698D-C784-4788-9CAB-3A7BC243D5F0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1483,7 +1492,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1491,31 +1500,31 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
       <c r="G1" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="B4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
